--- a/sources/bd.xlsx
+++ b/sources/bd.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcarr\Desktop\ProG\genesis\ordenes\management\commands\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcarr\Desktop\ProG\genesis\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A39FF5-F21A-4F91-B344-AD4DA3AC04B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2437439D-7641-460C-A329-FFF1B2FBE1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>LISTADO DE ORDENES DE TRABAJOS</t>
   </si>
@@ -117,6 +117,18 @@
   </si>
   <si>
     <t>Prueba</t>
+  </si>
+  <si>
+    <t>pr2</t>
+  </si>
+  <si>
+    <t>ASFAS</t>
+  </si>
+  <si>
+    <t>DSFA</t>
+  </si>
+  <si>
+    <t>dsgg</t>
   </si>
 </sst>
 </file>
@@ -515,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:M12"/>
+  <dimension ref="A3:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -748,6 +760,38 @@
         <v>46172</v>
       </c>
     </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B13">
+        <v>20250007</v>
+      </c>
+      <c r="C13">
+        <v>20256154</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>46165</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
